--- a/templates/bir-receipts-template.xlsx
+++ b/templates/bir-receipts-template.xlsx
@@ -2023,7 +2023,7 @@
   <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.54296875" customWidth="1"/>
+    <col min="1" max="1" width="8.4921875" customWidth="1"/>
     <col min="2" max="2" width="12.1796875" customWidth="1"/>
     <col min="4" max="4" width="10.54296875" customWidth="1"/>
     <col min="5" max="5" width="16.54296875" customWidth="1"/>
